--- a/docs/paper_results_tables.xlsx
+++ b/docs/paper_results_tables.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main results" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablations" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do not claim" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numbers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main results" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablations" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do not claim" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,7 +33,17 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0017203A"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="005B6579"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -96,12 +109,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -482,6 +512,1518 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H104"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sleep-EDF-78 — subject-disjoint 5-fold — accuracy %, FINE-TUNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Input tokens</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Pretrained</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>No pretrain</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Δ pretrain</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Raw features → logreg</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>HGB</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>SOTA (unverified)</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Pretrain seeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>tf64 (2×64)</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>81–85</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>DE (2×5)</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>81–85</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>raw 200 ms (2×20)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>81–85</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>raw per-electrode (1×20)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>81–85</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>± over seeds: tf64 0.4 / 0.2; DE 0.3 / 0.5. κ: tf64 .71 / .69; DE .672 / .645; raw .676 / .658.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Sleep-EDF-78 — Cohen's κ, FINE-TUNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Input tokens</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Pretrained</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>No pretrain</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Raw features → logreg</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>SOTA (unverified)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>tf64</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>0.77–0.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>0.77–0.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>raw 200 ms</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>0.676</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>0.77–0.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CHB-MIT seizure detection — leave-one-patient-out (24 patients)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>bal-acc %</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>ROC-AUC</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Seeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Fine-tuned — pretrained</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Fine-tuned — pretrained (Jul, 3-seed mean)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Fine-tuned — no pretrain</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Fine-tuned — no pretrain (Jul, 3-seed mean)</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Fine-tuned — latent objective</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Frozen — pretrained</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Frozen — no pretrain</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Raw DE → logreg</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Raw DE → HGB</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SOTA cross-patient (unverified)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>0.91–0.99</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Per-patient sd ±12–16 bal-acc: the three fine-tuned arms are indistinguishable. tf64 gives no headroom on this task (linear 72.4 = 72.4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Streaming evaluation — Sleep-EDF-78, DE tokens, FINE-TUNED (accuracy %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Offline (whole window)</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Online (past only)</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Tokens per decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Causal — no pretrain</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Bidirectional twin — no pretrain</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Causal — latent</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Causal — pretrained</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>1 seed, 5 folds. Causal beats bidirectional online by +2.8 (no pretrain) / +5.0 (pretrained).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Frozen-probe settings (never fine-tuned) — accuracy % unless noted</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Pretrained</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>No pretrain</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Raw features → logreg</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Seeds</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Emotion SEED-IV, smoothed</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>56.9</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Emotion SEED-IV, un-smoothed</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Motor imagery BCI-IV-2a</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Seizure prediction — bal-acc</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Seizure prediction — AUC</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Ablation — pretraining Δ (pretrained − no pretrain): frozen probe vs fine-tuned</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Frozen Δ</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Fine-tuned Δ</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Inflation ×</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Sleep DE</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Sleep tf64</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Sleep raw</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Seizure DE</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C50" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>Ablation — pretraining objective (Sleep DE, fine-tuned accuracy %, seed 42)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Objective</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Input-space PC (next 16 tokens, MSE)</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>75.40000000000001</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Latent targets (JEPA/data2vec)</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>74.09999999999999</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Latent — delta targets</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>73.90000000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Latent — cosine, no normalisation</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>72.7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Latent — variance term</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>73.2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Latent — EMA 0.99</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Latent — p_out 4</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>No pretraining</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>73.2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>4-seed means: input-PC 75.5, latent 73.7, no pretrain 73.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>Ablation — linear saturation of the input features</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Features</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Logistic regression</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>HGB</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Headroom (best − linear)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Sleep DE (acc)</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="C66" s="5" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Sleep tf64 (acc)</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Seizure DE (bal-acc)</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="C68" s="5" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>74</v>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>Seizure tf64 (bal-acc)</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="C69" s="5" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Seizure DE (AUC)</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="D70" s="6" t="n">
+        <v>0.851</v>
+      </c>
+      <c r="E70" s="6" t="n">
+        <v>0.044</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>Seizure tf64 (AUC)</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>0.849</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>Ablation — dimension-matched control (frozen probe, accuracy %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Raw features</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Random 256-d projection</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Pretrained encoder</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Δ vs projection</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Concat raw ‖ encoder</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>Sleep DE</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="C75" s="5" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>73.3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Sleep tf64</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="C76" s="5" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>77.40000000000001</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>Emotion SEED-IV smoothed</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="C77" s="5" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>60</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Motor imagery</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="C78" s="5" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="E78" s="6" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>Ablation — structured vs per-electrode raw tokens (Sleep, fine-tuned accuracy %, 1 seed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Arm</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Structured (2×20)</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Per-electrode (1×20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Pretrained</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="C82" s="5" t="n">
+        <v>76.40000000000001</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Latent</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>No pretrain</t>
+        </is>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="C84" s="5" t="n">
+        <v>74.59999999999999</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>Ablation — label fraction (Sleep DE, Δ pretrained − no pretrain, accuracy points)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Training labels</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>Frozen Δ</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Fine-tuned Δ</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>1 %</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>5 %</t>
+        </is>
+      </c>
+      <c r="B89" s="5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>10 %</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>100 %</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>Reference — Phase 1 vs Phase 2 (emotion, frozen probe, accuracy %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>SEED-V</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>SEED-IV</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Chance</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Univariate TimesFM (Phase 1)</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>23–25</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>26–28</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>20 / 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Structured patch, no pretrain</t>
+        </is>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="C96" s="5" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>20 / 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>Structured patch, pretrained</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="C97" s="5" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>20 / 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Raw DE → logreg</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="C98" s="5" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>20 / 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>Raw DE + per-series instance norm</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="C99" s="5" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>20 / 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>Reference — PC-SSL leakage audit (accuracy %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Same code, random window split</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Same code, trial-disjoint split</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>Raw DE → logreg</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>SEED-V</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="C103" s="5" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>51.4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>SEED-IV</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="C104" s="5" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>62.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -492,272 +2034,272 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Final method (proposed for the paper)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Alternatives we measured</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Decision / note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>A. What the model is</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Structured-token causal decoder transformer: TimesFM-2.5 decoder layers (RoPE, SDPA), d=256, 6 layers, 8 heads, ~2.4M params; linear token embedder; per-epoch classification head.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Frozen TimesFM-2.5 stack (E1b), frozen random 1280x20 stack (F3): neither beats the small from-scratch stack.</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Fixed.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Token</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>One token = one labelled epoch; the whole (channels x features) matrix, flattened. FINAL: tf64 = 64 log-spaced Welch log-power bins per channel (sleep 2x64=128-d).</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>DE (5 bands/channel; the proposal's token) -&gt; 75.5 sleep; raw 200 ms tokens (2x20 samples, 150 tokens/epoch) -&gt; 75.5; per-electrode raw -&gt; 76.4.</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>DISCUSS: tf64 is +2.3 over DE on sleep but gives no headroom on seizure (tf64 ladder on CHB-MIT skipped). Paper can present DE as the proposal's token and tf64 as the improved front end.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Normalisation</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Fixed per-(channel,feature) corpus standardisation; NO per-series instance norm (RevIN).</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Instance norm collapses raw DE to chance (51.4-&gt;18.0 SEED-V, 62.8-&gt;26.8 SEED-IV).</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Fixed (Phase-1 lesson).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Causality</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Causal (each epoch sees only the past) -&gt; streaming-capable, 1 token per decision with a KV cache.</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Bidirectional twin: +0.9 offline, -2.8/-5.0 online.</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Fixed; the streaming result is a selling point.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>B. Training</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Pretraining (the proposal's contribution)</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Input-space predictive coding: predict the next 16 tokens (multi-step MSE), 60 epochs (DE/tf64) / 10 epochs (raw), single dataset, no labels. Worth +2.5 (DE) / +0.85 (tf64) / +1.2 (raw) on sleep, ~0 on seizure, fine-tuned.</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Latent-target (JEPA/data2vec) objective and 5 variants: worse than input-PC (73.7 vs 75.5 sleep); masked reconstruction (F9): same null on emotion. Random init: within 0.85-2.5 points.</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>DISCUSS: keep pretraining as part of 'the method' (small positive on sleep) or present the model as trained from scratch with pretraining as an ablation? Recommendation: report both columns everywhere; call the final method 'pretrained' only if we keep the sleep +0.85..+2.5 as a claim.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Downstream training</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>End-to-end fine-tuning (encoder + head), class-weighted CE, AdamW 1e-4, nights/files chunked (400 epochs DE/tf64; 20 epochs raw), 8 epochs (sleep DE/tf64), 3 (raw), 4 (seizure).</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Frozen encoder + logistic regression (the July protocol): inflates pretraining 3-12x.</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Fixed: fine-tuned numbers only in the paper; frozen shown once as the inflation example.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>C. Evaluation</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Sleep-EDF Cassette, 153 nights / 78 subjects / 195k epochs, Fpz-Cz + Pz-Oz, 5 classes (W/N1/N2/N3/REM), 30-min wake trimming, subject-disjoint 5-fold (seed 42 split); acc / macro-F1 / kappa; pretraining seeds 42,1,2,3.</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr"/>
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Fixed.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Seizure</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>CHB-MIT, 24 patients / 682 files / 1.76M 2-s epochs (0.32% seizure), 18-ch bipolar core montage, leave-one-patient-out; bal-acc / sens / spec / ROC-AUC, class-weighted; per-patient paired tests.</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr"/>
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Fixed.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Emotion / MI</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>SEED-IV (smoothed + un-smoothed), PC-SSL subject-dependent folds; BCI-IV-2a session hold-out. Frozen-probe only (never fine-tuned).</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr"/>
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>DISCUSS: keep as 'where the encoder does not help' (frozen) or drop/appendix.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Controls reported with every result</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>matched random-init (same architecture, same seed); raw-features-&gt;logreg; best non-deep baseline (HGB); dimension-matched random projection (frozen).</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr"/>
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Fixed.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>D. Naming</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>Names in tables</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>PhysioFM (pretrained) = physiofm_pc; PhysioFM (no pretrain) = physiofm_rand; PhysioFM (latent) = physiofm_latent; raw features -&gt; logreg = raw_de / raw_tf64.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr"/>
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>DISCUSS: 'PhysioFM' implies a foundation model (no joint pretraining, no zero-shot transfer was done). Keep or rename?</t>
         </is>
@@ -774,7 +2316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -800,885 +2342,885 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Dataset / protocol</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Input tokens</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Final method: PhysioFM (pretrained)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>PhysioFM (no pretrain)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Pretraining delta</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>raw features -&gt; logreg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Best non-deep baseline (HGB)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Published SOTA (UNVERIFIED web figures)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Seeds</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="8" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="8" t="inlineStr">
         <is>
           <t>Include in paper?</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="8" t="inlineStr">
         <is>
           <t>Notes for discussion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Per-epoch tasks, FINE-TUNED (the protocol we report)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Sleep staging</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Sleep-EDF-78, subject-disjoint 5-fold</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>tf64 (2x64)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>acc % (kappa)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>77.9 +- 0.4 (k .71)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>77.0 +- 0.2 (k .69)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>+0.85 (sign consistent 4/4 seeds)</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>72.8 (k .64)</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>81-85 (k .77-.83) raw-signal models</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>4 pretraining seeds</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="10" t="inlineStr">
         <is>
           <t>results/phase4/gate0/sleep_edf_tf64/finetune.csv; EXP-0020</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>Headline number. Below SOTA by 3-7 with 2.4M params / spectral tokens.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Sleep staging</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Sleep-EDF-78, subject-disjoint 5-fold</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>DE (2x5) — the proposal's token</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>acc % (kappa)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>75.5 +- 0.3 (k .672)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>73.1 +- 0.5 (k .645)</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>+2.5 (4/4 seeds)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>67.9 (k .575)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>69.6</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>81-85</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>4 pretraining seeds</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>results/phase4/gate1/sleep_edf/finetune.csv; EXP-0017 4b, EXP-0021</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>The proposal's pipeline; shows the DE-&gt;tf64 gain (+2.3) and that pretraining shrinks as input gets richer.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Sleep staging</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Sleep-EDF-78, subject-disjoint 5-fold</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>raw EEG 200 ms (2x20), 150 tok/epoch</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>acc % (kappa)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>75.5 (k .676)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>74.2 (k .658)</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>+1.2 (frozen: +14.7)</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>81-85</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>1 seed; 10 pretrain + 3 FT epochs</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="10" t="inlineStr">
         <is>
           <t>results/phase4/gate2/sleep_edf_raw/finetune.csv; EXP-0022</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="12" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>Parity with DE, below tf64 at this budget. Single seed — say so, or run 2 more seeds (~1.5 h on a pod).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Sleep staging — streaming</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Sleep-EDF-78, same folds, DE tokens</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>acc % online (only past visible) / offline</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>75.4 / 75.4 (causal, pretrained)</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>73.2 / 73.2 (causal, no pretrain); bidirectional twin 70.4 online / 74.1 offline</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>causal beats bidirectional online by +2.8 (no pretrain) / +5.0 (pretrained)</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>1 seed, 5 folds</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>results/phase4/gate3/streaming.csv; EXP-0023</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="M6" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>The 'defensible claim' of the causal design; 1 token/decision (KV cache) vs 190.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Seizure detection</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>CHB-MIT, 24 patients, leave-one-patient-out</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>DE (18x5)</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>bal-acc % / ROC-AUC</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>78.4 / .863 (Aug seed 42); 78.2 / .867 (Jul, 3 seeds)</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>80.2 / .874 (seed 42); 79.1 / .860 (Jul, 3 seeds)</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>≈ 0 (within +-12 per-patient sd)</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>72.4 / .806</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>74.0 / .851</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>AUC .91-.99 (cross-patient; verify)</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>3 seeds (Jul) + 1 (Aug)</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="10" t="inlineStr">
         <is>
           <t>results/phase3/f17/f17_ft_seed*.csv; results/phase4/gate1/chbmit/finetune.csv; EXP-0017 4c, EXP-0021</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="M7" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>Architecture beats raw-DE by ~+6 bal-acc / +.06 AUC; pretraining adds nothing. tf64 gives no headroom here (linear 72.4 = 72.4).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Frozen-probe settings (never fine-tuned) — report as scope / failure cases, not headlines</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Emotion, smoothed</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>SEED-IV de_LDS, PC-SSL subject-dependent folds</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>DE (62x5)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>acc %</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>56.9</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>+2.4</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>62.8</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>(nonlinear &lt;= linear, F10)</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>84.5 published -&gt; 44.7 clean (leakage)</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>3 seeds</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="10" t="inlineStr">
         <is>
           <t>results/phase3/parity; EXP-0016</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M9" s="12" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>Pretrained = random 256-d projection (dim-matched -0.2). Below raw features.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Emotion, un-smoothed</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>SEED-IV de_movingAve, same folds</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>DE (62x5)</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>acc %</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>51.7</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>40.7</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>+11.0 (frozen only)</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>55.3</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>3 seeds</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L10" s="10" t="inlineStr">
         <is>
           <t>results/phase3/parity; EXP-0016</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="M10" s="12" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr">
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>The 'smoothing flip'; still below raw features.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Motor imagery</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>BCI-IV-2a, session hold-out, 9 subj</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>DE (22x5)</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>acc %</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>41.7</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>43.5</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>-1.8</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>~70-85 (raw-signal)</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>3 seeds</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="10" t="inlineStr">
         <is>
           <t>results/phase3/parity/f16*; EXP-0014/0016</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>Encoder hurts (dim-matched -9.3). Trial-constant labels.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Seizure prediction (pre-ictal vs interictal)</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>CHB-MIT, patient-specific leave-one-seizure-out, 21 patients / 140 events</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>DE (18x5)</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>bal-acc % / AUC</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>66.8 / .769</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>71.3 / .793</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>-4.6 / -.024</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>65.2 / .710</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>1 seed</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L12" s="10" t="inlineStr">
         <is>
           <t>FINAL_REPORT §5; EXP-0018 (CSV on pod only)</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" s="13" t="inlineStr">
         <is>
           <t>no / appendix</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>Ran as the falsification test of the 'objective misalignment' mechanism; random-init won. Not comparable to detection.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Reference points</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Phase 1: univariate TimesFM</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>SEED-IV/V, same folds</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>each (channel,band) trace as a scalar series</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>acc %</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>20-28 (chance)</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>51.4 / 62.8</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>docs/PHASE1.md</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M14" s="11" t="inlineStr">
         <is>
           <t>yes (one line)</t>
         </is>
       </c>
-      <c r="N14" s="3" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Why structured patching exists: RevIN + flattening destroy the signal. Structured: 46-61.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Leakage audit of PC-SSL</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>SEED-V / SEED-IV, PC-SSL code</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>acc %</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>published 92.4 / 84.5; leaky re-run 65.8 / 70.4; clean trial-disjoint 39.8 / 44.7</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>51.4 / 62.8</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>results/phase2/followup/f12; EXP-0008</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M15" s="11" t="inlineStr">
         <is>
           <t>yes (one paragraph)</t>
         </is>
       </c>
-      <c r="N15" s="3" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>~80% temporal-neighbour leakage. A replication of Brookshire et al. 2024 — cite it.</t>
         </is>
@@ -1694,7 +3236,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1717,1035 +3259,1035 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Ablation / control</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Question it answers</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Arms and numbers</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Delta / effect</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>Seeds</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>Include in paper?</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>A. Does pretraining help? (the contribution under test)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Pretrained vs matched random-init, FINE-TUNED</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Is predictive-coding pretraining worth anything under the protocol competitors use?</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Sleep DE / tf64 / raw / per-electrode; seizure DE</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>sleep DE 75.5 vs 73.1; tf64 77.9 vs 77.0; raw 75.5 vs 74.2; per-electrode 76.4 vs 74.6; seizure 78.4/.863 vs 80.2/.874 (Jul 3-seed 78.2 vs 79.1)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>+2.5 / +0.85 / +1.2 / +1.8 on sleep; ≈ 0 on seizure</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>4 / 4 / 1 / 1 / 3+1</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Small positive on sleep, shrinking as input gets richer; null on seizure</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>gate1/sleep_edf/finetune.csv, gate0/sleep_edf_tf64/finetune.csv, gate2/*, gate1/chbmit/finetune.csv, f17_ft_seed*</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>THE central ablation; must be in the main table.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Frozen probe vs fine-tuned (evaluation protocol)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>How much did the frozen-probe protocol inflate pretraining?</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>same as 1</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>frozen gaps: DE +9.8, tf64 +11.2, raw +14.7, seizure +8.1; fine-tuned gaps: +2.5, +0.85, +1.2, ≈0</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>inflation 3-12x</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Frozen probes measure the poverty of a random-init feature extractor, not the value of pretraining</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>EXP-0017 4b-c, EXP-0020-0022</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Methodological finding; one figure (bars frozen vs fine-tuned).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Dimension-matched control (raw features -&gt; random 256-d nonlinear projection), frozen</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Is the frozen 'gain' just more dimensions?</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>sleep DE/tf64, emotion, MI</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>sleep DE: rand-proj 69.3 vs PC 72.6 (+3.3); tf64: 73.3 vs 76.75 (+3.5); emotion 60.2 vs 60.0 (-0.2); MI 49.9 vs 40.6 (-9.3); concat raw+PC: +5.4 sleep, -0.3 emotion, -7.3 MI</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>see arms</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Pretrained encoder adds information only on sleep; on emotion it equals a random map</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>results/phase3/diagnose_encoder.csv; gate0/diagnose_encoder_tf64.csv; EXP-0017 §3</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Label fraction under fine-tuning</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Does the advantage grow when labels are scarce (the SSL signature)?</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>sleep DE, 1/5/10/100% of training labels</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>frozen gap 12.7/11.8/10.8/9.8; fine-tuned gap 1.9/2.4/2.4/2.2</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>flat fine-tuned</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Label-efficiency signature is a frozen-probe artefact (retracted claim)</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>results/phase3/f13/f13_sleep_ft_labelcurve.csv; EXP-0017 4d</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="12" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>Mention as part of #2 or drop; do NOT claim 20x/100x.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>B. Which pretraining objective?</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Input-space PC vs latent-target PC (JEPA/data2vec style)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Is input-space MSE the reason pretraining fails (R2)?</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>sleep DE (4 seeds), seizure, tf64, raw</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>sleep DE: input 75.5 vs latent 73.7 vs rand 73.1; seizure 78.4 vs 79.7 vs 80.2; tf64 77.9 vs 77.3 vs 77.0; raw 75.5 vs 74.7 vs 74.2</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>latent -1.9 vs input-PC on sleep DE; ≈ random elsewhere</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>4/1/4/1</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Latent targets do not help; objective degenerates into smoothness on per-epoch corpora (skill &lt;= 0)</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>gate1/*, EXP-0021</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="11" t="inlineStr">
         <is>
           <t>yes (short)</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Latent objective variants</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Any latent variant that works?</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>sleep DE, seed 42, fine-tuned</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>delta targets 73.9; cosine/no-norm 72.7 (collapses); variance term 73.2; EMA .99 74.0; p_out 4 74.0 (input-PC 75.4, rand 73.2)</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>all at random-init level</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>gate1/sleep_edf/finetune.csv (variant rows); EXP-0021</t>
         </is>
       </c>
-      <c r="J9" s="7" t="inlineStr">
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>appendix</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr"/>
+      <c r="K9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Masked reconstruction vs forecasting (F9)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Is it the temporal objective?</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>emotion smoothed / un-smoothed, frozen</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>both objectives null on smoothed, both ~+9 over random on un-smoothed</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>no difference</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Not the specific objective</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>results/phase2/followup/f9; EXP-0011</t>
         </is>
       </c>
-      <c r="J10" s="7" t="inlineStr">
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>appendix</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="K10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Pretext diagnostics</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Is the pretext learned, and does pretext skill predict transfer?</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>all datasets</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>input-space model/persistence: sleep .60, seizure .57, emo-raw .44, MI .35, emo-smooth 27.8 (degenerate); latent skill vs best trivial: sleep -0.2, seizure -0.6, tf64 ~0, raw +0.36, emotion +0.4/+0.6, MI +0.6</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>skill anti-correlates with transfer (both objectives)</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Pretext learned but misaligned; mechanism's falsifiable prediction (seizure prediction) failed</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>results/phase3/diagnose_pretext.csv; gate1/diagnose_pretext_latent.csv; EXP-0017 4e, 0018, 0021</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>Scientifically the most interesting part; fits Option B/C.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>C. Which input tokens?</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>DE vs tf64 vs raw tokens (architecture, no pretraining)</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>What does the input representation buy the architecture?</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>sleep, fine-tuned</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>random-init: DE 73.1, tf64 77.0, raw 74.2; linear ceilings: DE 67.9, tf64 72.8</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>tf64 +3.9 over DE for the same architecture</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>4/4/1</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>tf64 is the better front end on sleep; none on seizure (linear 72.4 = 72.4)</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>gate0/saturation_*.csv; finetune csvs; EXP-0020</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>Gate 0.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Linear-saturation test (logreg vs MLP vs HGB)</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Is there nonlinear headroom in the features at all?</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>sleep + seizure, DE + tf64</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>sleep DE 67.9/67.2/69.6; tf64 72.8/71.9/75.2; seizure DE 72.4/69.5/74.0 (AUC .807/.824/.851); tf64 72.4/69.9/72.6</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>headroom +1.7 -&gt; +2.3 sleep; +1.6 -&gt; +0.2 seizure</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>5 folds / 24 pat</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Little headroom on DE; tf64 adds some on sleep only</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>gate0/saturation_*; EXP-0010 (emotion), EXP-0020</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
         <is>
           <t>yes (one table)</t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="K14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Structured multi-channel tokens vs per-electrode decomposition (BrainGPT-style)</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Is spatial structure in the token what matters?</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>sleep raw tokens, 2 channels</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>structured 75.5/74.7/74.2 vs per-electrode 76.4/75.5/74.6 (PC/latent/rand, fine-tuned); frozen 70.8 vs 72.7</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>per-electrode &gt;= structured by ~1</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Not supported on 2-channel sleep; needs a many-channel corpus</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>gate2/*; EXP-0022</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J15" s="12" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="10" t="inlineStr">
         <is>
           <t>Honest limitation; do NOT claim structured &gt; per-electrode.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Smoothing flip (LDS-smoothed vs un-smoothed DE)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Does smoothing hide the dynamics PC needs?</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>SEED-IV emotion, frozen, same trials</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>within-trial variance 0.08% vs 17.6%; PC - rand +2.4 vs +11.0</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>+8.6 from removing smoothing</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Pretraining needs dynamics in the tokens — but still below raw features</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>EXP-0001, EXP-0016</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr"/>
+      <c r="K16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Context length / horizon (F5) and scale (F6)</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Do longer context and multi-horizon help?</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>un-smoothed SEED-IV, frozen GRU readout</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>PC-rand gap grows with p_in (5.3 -&gt; 18.1 at p_in 8/p_out 16); scale-stable 1M-15M (5 -&gt; 13 -&gt; 13)</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>Only on un-smoothed DE; frozen readout</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>EXP-0005, EXP-0006</t>
         </is>
       </c>
-      <c r="J17" s="7" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>appendix</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="K17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>D. Architecture controls</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Causal vs bidirectional twin, offline vs online</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>What does causality cost / buy?</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>sleep DE, fine-tuned, same folds</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>causal rand 73.2/73.2; bidir rand 74.1/70.4; causal latent 74.1/74.1; causal PC 75.4/75.4</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>offline -0.9; online +2.8 (+5.0 pretrained); 1 vs 190 tokens per decision</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Causal wins under a streaming constraint</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>gate3/streaming.csv; EXP-0023</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="11" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>Gate 3.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>Per-series instance norm (RevIN) control</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Why Phase 1 failed / why no instance norm</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>emotion raw DE -&gt; logreg</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>SEED-V 51.4 -&gt; 18.0; SEED-IV 62.8 -&gt; 26.8 (chance 20/25)</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>collapse to chance</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>Instance norm deletes the discriminative absolute level</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>docs/PHASE2.md E3.2</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="11" t="inlineStr">
         <is>
           <t>yes (one line)</t>
         </is>
       </c>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="K20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>Frozen random stack vs frozen TimesFM stack (F3); matched MLP head (F4)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Do TimesFM weights transfer? Is the head the limiter?</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>emotion, frozen</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>random 1280x20 stack 47.3/58.9 vs TimesFM 43.3/60.4; MLP head stays in the 41-55 band</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>TimesFM weights add nothing; head not the lever</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>EXP-0003, EXP-0004</t>
         </is>
       </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>appendix</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="K21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Order-shuffle control</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Is the sleep gain temporal?</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>sleep frozen; emotion/MI</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>sleep PC 72.6 -&gt; 67.4 (= raw-DE level), raw unchanged; on trial-constant-label tasks shuffling HELPS (+7.4 emotion) -&gt; uninterpretable there</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>-5.2 on sleep</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>Frozen sleep gain is temporal; control valid only for per-epoch labels</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>EXP-0009 4e, EXP-0016</t>
         </is>
       </c>
-      <c r="J22" s="7" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>appendix</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Data-only predictability (tau) vs gain</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Can a raw-data score predict the SSL gain?</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>5 settings</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>MI has the highest tau (0.27) and no gain; sleep the lowest among positives and the largest frozen gain</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>no correlation</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>No (kills the 'temporal learnability' framing)</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>results/phase3/temporal_structure.csv; EXP-0016</t>
         </is>
       </c>
-      <c r="J23" s="6" t="inlineStr">
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2758,7 +4300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2774,242 +4316,242 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Statement</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Why it is out</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>What we say instead</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Pretraining gives +9.8 (sleep) / +14.5 / +8.1 (seizure)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>frozen-probe numbers</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>fine-tuned: +2.5 / ≈0</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>report fine-tuned; frozen once as the inflation example</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>20x / 100x label efficiency</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>frozen-probe artefact</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>fine-tuned gap flat +1.9..+2.4 at 1-100% labels</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>drop</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>PC helps in proportion to temporal structure</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>MI has the highest predictability and no gain; seizure prediction falsified the refined version</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>EXP-0016, EXP-0018</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>drop</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>The objective-misalignment mechanism explains the failure</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>its falsifiable prediction (seizure prediction) failed</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>rand .793 &gt; PC .769 AUC</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>report the diagnostic (pretext skill anti-correlates with transfer) without asserting the mechanism</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Structured spatial patching beats per-electrode decomposition</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>2-channel sleep shows the opposite</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>76.4 vs 75.5</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>limitation: needs a many-channel corpus</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>A foundation model / cross-task transfer</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>joint multi-dataset pretraining and zero-shot transfer were never run</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>proposal Phase 3</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>future work; consider renaming</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Beats / matches published SOTA</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>below on every task; SOTA figures unverified</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>sleep 77.9 vs 81-85; seizure AUC .87 vs .91-.99</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>honest positioning table after verifying numbers; emphasise 2.4M params, spectral tokens, streaming</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>The leakage audit is a new finding</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Brookshire et al. 2024 documented EEG segment-split leakage with similar numbers</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>ICML_proposal.md §B</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>replication + mechanism, cite Brookshire</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Latent-target / raw-EEG / richer tokens rescue pretraining</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Gates 0-2</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>+0.85 / +1.2 / latent -1.9</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>state as tested and negative</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Seizure prediction is a result</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>single seed, patient-specific, run only as a falsification test</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>EXP-0018</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>appendix at most</t>
         </is>

--- a/docs/paper_results_tables.xlsx
+++ b/docs/paper_results_tables.xlsx
@@ -23,13 +23,17 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000E5C5B"/>
     </font>
     <font>
       <b val="1"/>
@@ -41,16 +45,16 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="000E5C5B"/>
+    </font>
+    <font>
       <i val="1"/>
       <color rgb="005B6579"/>
       <sz val="9"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000E5C5B"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +64,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="0017203A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8EBE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF1F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -75,11 +89,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F9E5E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EEF1F6"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,42 +118,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -512,7 +534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H104"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -528,1488 +550,1495 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>FINAL METHOD = green cells: structured tokens (tf64 on sleep; DE on CHB-MIT — tf64 not run there) + causal decoder + input-space PC pretraining, fine-tuned end-to-end. Grey = its matched no-pretrain control (same architecture, random init).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Sleep-EDF-78 — subject-disjoint 5-fold — accuracy %, FINE-TUNED</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Input tokens</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Pretrained</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>No pretrain</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Δ pretrain</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Raw features → logreg</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>HGB</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>SOTA (unverified)</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Pretrain seeds</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>tf64 (2×64)</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B5" s="6" t="n">
         <v>77.90000000000001</v>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C5" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D5" s="8" t="n">
         <v>0.85</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E5" s="9" t="n">
         <v>72.8</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F5" s="9" t="n">
         <v>75.2</v>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>81–85</t>
         </is>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H5" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>DE (2×5)</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B6" s="9" t="n">
         <v>75.5</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C6" s="9" t="n">
         <v>73.09999999999999</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D6" s="8" t="n">
         <v>2.5</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E6" s="9" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F6" s="9" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>81–85</t>
         </is>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="H6" s="8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>raw 200 ms (2×20)</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B7" s="9" t="n">
         <v>75.5</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C7" s="9" t="n">
         <v>74.2</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D7" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>81–85</t>
         </is>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H7" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>raw per-electrode (1×20)</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B8" s="9" t="n">
         <v>76.40000000000001</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C8" s="9" t="n">
         <v>74.59999999999999</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D8" s="8" t="n">
         <v>1.8</v>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>81–85</t>
         </is>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="H8" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>± over seeds: tf64 0.4 / 0.2; DE 0.3 / 0.5. κ: tf64 .71 / .69; DE .672 / .645; raw .676 / .658.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Sleep-EDF-78 — Cohen's κ, FINE-TUNED</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Input tokens</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Pretrained</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>No pretrain</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Raw features → logreg</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>SOTA (unverified)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>tf64</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B13" s="11" t="n">
         <v>0.71</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C13" s="12" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D13" s="8" t="n">
         <v>0.64</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>0.77–0.83</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B14" s="8" t="n">
         <v>0.672</v>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C14" s="8" t="n">
         <v>0.645</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D14" s="8" t="n">
         <v>0.575</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>0.77–0.83</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>raw 200 ms</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B15" s="8" t="n">
         <v>0.676</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C15" s="8" t="n">
         <v>0.658</v>
       </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>0.77–0.83</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>CHB-MIT seizure detection — leave-one-patient-out (24 patients)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Arm</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>bal-acc %</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>ROC-AUC</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Seeds</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Fine-tuned — pretrained</t>
         </is>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B19" s="6" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C19" s="11" t="n">
         <v>0.863</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D19" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Fine-tuned — pretrained (Jul, 3-seed mean)</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B20" s="9" t="n">
         <v>78.2</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C20" s="8" t="n">
         <v>0.867</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D20" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Fine-tuned — no pretrain</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n">
+      <c r="B21" s="7" t="n">
         <v>80.2</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C21" s="12" t="n">
         <v>0.874</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D21" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Fine-tuned — no pretrain (Jul, 3-seed mean)</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B22" s="9" t="n">
         <v>79.09999999999999</v>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C22" s="8" t="n">
         <v>0.86</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D22" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Fine-tuned — latent objective</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B23" s="9" t="n">
         <v>79.7</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C23" s="8" t="n">
         <v>0.879</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D23" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Frozen — pretrained</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B24" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C24" s="8" t="n">
         <v>0.852</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D24" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Frozen — no pretrain</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n">
+      <c r="B25" s="9" t="n">
         <v>67.5</v>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C25" s="8" t="n">
         <v>0.741</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D25" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Raw DE → logreg</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B26" s="9" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C26" s="8" t="n">
         <v>0.806</v>
       </c>
-      <c r="D24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="D26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Raw DE → HGB</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B27" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C27" s="8" t="n">
         <v>0.851</v>
       </c>
-      <c r="D25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="D27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>SOTA cross-patient (unverified)</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>0.91–0.99</t>
         </is>
       </c>
-      <c r="D26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="D28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Per-patient sd ±12–16 bal-acc: the three fine-tuned arms are indistinguishable. tf64 gives no headroom on this task (linear 72.4 = 72.4).</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Streaming evaluation — Sleep-EDF-78, DE tokens, FINE-TUNED (accuracy %)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Arm</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Offline (whole window)</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Online (past only)</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>Tokens per decision</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Causal — no pretrain</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B33" s="7" t="n">
         <v>73.2</v>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C33" s="7" t="n">
         <v>73.2</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D33" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Bidirectional twin — no pretrain</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B34" s="9" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C34" s="9" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D34" s="8" t="n">
         <v>190</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Causal — latent</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B35" s="9" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C35" s="9" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D35" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Causal — pretrained</t>
         </is>
       </c>
-      <c r="B34" s="5" t="n">
+      <c r="B36" s="6" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C36" s="6" t="n">
         <v>75.40000000000001</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D36" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>1 seed, 5 folds. Causal beats bidirectional online by +2.8 (no pretrain) / +5.0 (pretrained).</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Frozen-probe settings (never fine-tuned) — accuracy % unless noted</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Pretrained</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>No pretrain</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>Raw features → logreg</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>Seeds</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Emotion SEED-IV, smoothed</t>
         </is>
       </c>
-      <c r="B39" s="5" t="n">
+      <c r="B41" s="9" t="n">
         <v>59.3</v>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C41" s="9" t="n">
         <v>56.9</v>
       </c>
-      <c r="D39" s="5" t="n">
+      <c r="D41" s="9" t="n">
         <v>62.8</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E41" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>Emotion SEED-IV, un-smoothed</t>
         </is>
       </c>
-      <c r="B40" s="5" t="n">
+      <c r="B42" s="9" t="n">
         <v>51.7</v>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C42" s="9" t="n">
         <v>40.7</v>
       </c>
-      <c r="D40" s="5" t="n">
+      <c r="D42" s="9" t="n">
         <v>55.3</v>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="E42" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Motor imagery BCI-IV-2a</t>
         </is>
       </c>
-      <c r="B41" s="5" t="n">
+      <c r="B43" s="9" t="n">
         <v>41.7</v>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C43" s="9" t="n">
         <v>43.5</v>
       </c>
-      <c r="D41" s="5" t="n">
+      <c r="D43" s="9" t="n">
         <v>51.1</v>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="E43" s="8" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Seizure prediction — bal-acc</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n">
+      <c r="B44" s="9" t="n">
         <v>66.8</v>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C44" s="9" t="n">
         <v>71.3</v>
       </c>
-      <c r="D42" s="5" t="n">
+      <c r="D44" s="9" t="n">
         <v>65.2</v>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="E44" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Seizure prediction — AUC</t>
         </is>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B45" s="8" t="n">
         <v>0.769</v>
       </c>
-      <c r="C43" s="6" t="n">
+      <c r="C45" s="8" t="n">
         <v>0.793</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D45" s="8" t="n">
         <v>0.71</v>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="E45" s="8" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Ablation — pretraining Δ (pretrained − no pretrain): frozen probe vs fine-tuned</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Frozen Δ</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Fine-tuned Δ</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Inflation ×</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Sleep DE</t>
         </is>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B49" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="C47" s="6" t="n">
+      <c r="C49" s="8" t="n">
         <v>2.5</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D49" s="8" t="n">
         <v>3.9</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Sleep tf64</t>
         </is>
       </c>
-      <c r="B48" s="5" t="n">
+      <c r="B50" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="C48" s="6" t="n">
+      <c r="C50" s="8" t="n">
         <v>0.85</v>
       </c>
-      <c r="D48" s="5" t="n">
+      <c r="D50" s="9" t="n">
         <v>13.2</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Sleep raw</t>
         </is>
       </c>
-      <c r="B49" s="5" t="n">
+      <c r="B51" s="9" t="n">
         <v>14.7</v>
       </c>
-      <c r="C49" s="6" t="n">
+      <c r="C51" s="8" t="n">
         <v>1.2</v>
       </c>
-      <c r="D49" s="5" t="n">
+      <c r="D51" s="9" t="n">
         <v>12.3</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Seizure DE</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B52" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="C50" s="6" t="n">
+      <c r="C52" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="D50" s="6" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="D52" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Ablation — pretraining objective (Sleep DE, fine-tuned accuracy %, seed 42)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Objective</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Accuracy</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>Input-space PC (next 16 tokens, MSE)</t>
         </is>
       </c>
-      <c r="B54" s="5" t="n">
+      <c r="B56" s="9" t="n">
         <v>75.40000000000001</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Latent targets (JEPA/data2vec)</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n">
+      <c r="B57" s="9" t="n">
         <v>74.09999999999999</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Latent — delta targets</t>
         </is>
       </c>
-      <c r="B56" s="5" t="n">
+      <c r="B58" s="9" t="n">
         <v>73.90000000000001</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>Latent — cosine, no normalisation</t>
         </is>
       </c>
-      <c r="B57" s="5" t="n">
+      <c r="B59" s="9" t="n">
         <v>72.7</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>Latent — variance term</t>
         </is>
       </c>
-      <c r="B58" s="5" t="n">
+      <c r="B60" s="9" t="n">
         <v>73.2</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Latent — EMA 0.99</t>
         </is>
       </c>
-      <c r="B59" s="5" t="n">
+      <c r="B61" s="9" t="n">
         <v>74</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>Latent — p_out 4</t>
         </is>
       </c>
-      <c r="B60" s="5" t="n">
+      <c r="B62" s="9" t="n">
         <v>74</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>No pretraining</t>
         </is>
       </c>
-      <c r="B61" s="5" t="n">
+      <c r="B63" s="9" t="n">
         <v>73.2</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="7" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
         <is>
           <t>4-seed means: input-PC 75.5, latent 73.7, no pretrain 73.1.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Ablation — linear saturation of the input features</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Features</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>Logistic regression</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>MLP</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>HGB</t>
         </is>
       </c>
-      <c r="E65" s="3" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>Headroom (best − linear)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>Sleep DE (acc)</t>
         </is>
       </c>
-      <c r="B66" s="5" t="n">
+      <c r="B68" s="9" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C68" s="9" t="n">
         <v>67.2</v>
       </c>
-      <c r="D66" s="5" t="n">
+      <c r="D68" s="9" t="n">
         <v>69.59999999999999</v>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="E68" s="8" t="n">
         <v>1.7</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>Sleep tf64 (acc)</t>
         </is>
       </c>
-      <c r="B67" s="5" t="n">
+      <c r="B69" s="9" t="n">
         <v>72.8</v>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C69" s="9" t="n">
         <v>71.90000000000001</v>
       </c>
-      <c r="D67" s="5" t="n">
+      <c r="D69" s="9" t="n">
         <v>75.2</v>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="E69" s="8" t="n">
         <v>2.3</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>Seizure DE (bal-acc)</t>
         </is>
       </c>
-      <c r="B68" s="5" t="n">
+      <c r="B70" s="9" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C70" s="9" t="n">
         <v>69.5</v>
       </c>
-      <c r="D68" s="5" t="n">
+      <c r="D70" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="E70" s="8" t="n">
         <v>1.6</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Seizure tf64 (bal-acc)</t>
         </is>
       </c>
-      <c r="B69" s="5" t="n">
+      <c r="B71" s="9" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C71" s="9" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="D69" s="5" t="n">
+      <c r="D71" s="9" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="E71" s="8" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>Seizure DE (AUC)</t>
         </is>
       </c>
-      <c r="B70" s="6" t="n">
+      <c r="B72" s="8" t="n">
         <v>0.8070000000000001</v>
       </c>
-      <c r="C70" s="6" t="n">
+      <c r="C72" s="8" t="n">
         <v>0.824</v>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="D72" s="8" t="n">
         <v>0.851</v>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="E72" s="8" t="n">
         <v>0.044</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>Seizure tf64 (AUC)</t>
         </is>
       </c>
-      <c r="B71" s="6" t="n">
+      <c r="B73" s="8" t="n">
         <v>0.8090000000000001</v>
       </c>
-      <c r="C71" s="6" t="n">
+      <c r="C73" s="8" t="n">
         <v>0.824</v>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D73" s="8" t="n">
         <v>0.849</v>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="E73" s="8" t="n">
         <v>0.04</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Ablation — dimension-matched control (frozen probe, accuracy %)</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>Raw features</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C76" s="4" t="inlineStr">
         <is>
           <t>Random 256-d projection</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
+      <c r="D76" s="4" t="inlineStr">
         <is>
           <t>Pretrained encoder</t>
         </is>
       </c>
-      <c r="E74" s="3" t="inlineStr">
+      <c r="E76" s="4" t="inlineStr">
         <is>
           <t>Δ vs projection</t>
         </is>
       </c>
-      <c r="F74" s="3" t="inlineStr">
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>Concat raw ‖ encoder</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
         <is>
           <t>Sleep DE</t>
         </is>
       </c>
-      <c r="B75" s="5" t="n">
+      <c r="B77" s="9" t="n">
         <v>67.90000000000001</v>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C77" s="9" t="n">
         <v>69.3</v>
       </c>
-      <c r="D75" s="5" t="n">
+      <c r="D77" s="9" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="E77" s="8" t="n">
         <v>3.3</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="F77" s="9" t="n">
         <v>73.3</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>Sleep tf64</t>
         </is>
       </c>
-      <c r="B76" s="5" t="n">
+      <c r="B78" s="9" t="n">
         <v>72.8</v>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C78" s="9" t="n">
         <v>73.3</v>
       </c>
-      <c r="D76" s="5" t="n">
+      <c r="D78" s="9" t="n">
         <v>76.8</v>
       </c>
-      <c r="E76" s="6" t="n">
+      <c r="E78" s="8" t="n">
         <v>3.5</v>
       </c>
-      <c r="F76" s="5" t="n">
+      <c r="F78" s="9" t="n">
         <v>77.40000000000001</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
         <is>
           <t>Emotion SEED-IV smoothed</t>
         </is>
       </c>
-      <c r="B77" s="5" t="n">
+      <c r="B79" s="9" t="n">
         <v>62.8</v>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C79" s="9" t="n">
         <v>60.2</v>
       </c>
-      <c r="D77" s="5" t="n">
+      <c r="D79" s="9" t="n">
         <v>60</v>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="E79" s="8" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="F79" s="9" t="n">
         <v>62.5</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="4" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>Motor imagery</t>
         </is>
       </c>
-      <c r="B78" s="5" t="n">
+      <c r="B80" s="9" t="n">
         <v>51.1</v>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C80" s="9" t="n">
         <v>49.9</v>
       </c>
-      <c r="D78" s="5" t="n">
+      <c r="D80" s="9" t="n">
         <v>40.6</v>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="E80" s="8" t="n">
         <v>-9.300000000000001</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F80" s="9" t="n">
         <v>43.8</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Ablation — structured vs per-electrode raw tokens (Sleep, fine-tuned accuracy %, 1 seed)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Arm</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>Structured (2×20)</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C83" s="4" t="inlineStr">
         <is>
           <t>Per-electrode (1×20)</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
         <is>
           <t>Pretrained</t>
         </is>
       </c>
-      <c r="B82" s="5" t="n">
+      <c r="B84" s="9" t="n">
         <v>75.5</v>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C84" s="9" t="n">
         <v>76.40000000000001</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>Latent</t>
         </is>
       </c>
-      <c r="B83" s="5" t="n">
+      <c r="B85" s="9" t="n">
         <v>74.7</v>
       </c>
-      <c r="C83" s="5" t="n">
+      <c r="C85" s="9" t="n">
         <v>75.5</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
         <is>
           <t>No pretrain</t>
         </is>
       </c>
-      <c r="B84" s="5" t="n">
+      <c r="B86" s="9" t="n">
         <v>74.2</v>
       </c>
-      <c r="C84" s="5" t="n">
+      <c r="C86" s="9" t="n">
         <v>74.59999999999999</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Ablation — label fraction (Sleep DE, Δ pretrained − no pretrain, accuracy points)</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Training labels</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Frozen Δ</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Fine-tuned Δ</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>1 %</t>
         </is>
       </c>
-      <c r="B88" s="5" t="n">
+      <c r="B90" s="9" t="n">
         <v>12.7</v>
       </c>
-      <c r="C88" s="6" t="n">
+      <c r="C90" s="8" t="n">
         <v>1.9</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>5 %</t>
         </is>
       </c>
-      <c r="B89" s="5" t="n">
+      <c r="B91" s="9" t="n">
         <v>11.8</v>
       </c>
-      <c r="C89" s="6" t="n">
+      <c r="C91" s="8" t="n">
         <v>2.4</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>10 %</t>
         </is>
       </c>
-      <c r="B90" s="5" t="n">
+      <c r="B92" s="9" t="n">
         <v>10.8</v>
       </c>
-      <c r="C90" s="6" t="n">
+      <c r="C92" s="8" t="n">
         <v>2.4</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>100 %</t>
         </is>
       </c>
-      <c r="B91" s="6" t="n">
+      <c r="B93" s="8" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="C91" s="6" t="n">
+      <c r="C93" s="8" t="n">
         <v>2.2</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Reference — Phase 1 vs Phase 2 (emotion, frozen probe, accuracy %)</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>SEED-V</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>SEED-IV</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D96" s="4" t="inlineStr">
         <is>
           <t>Chance</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>Univariate TimesFM (Phase 1)</t>
         </is>
       </c>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>23–25</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C97" s="8" t="inlineStr">
         <is>
           <t>26–28</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>20 / 25</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
         <is>
           <t>Structured patch, no pretrain</t>
         </is>
       </c>
-      <c r="B96" s="5" t="n">
+      <c r="B98" s="9" t="n">
         <v>48.6</v>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C98" s="9" t="n">
         <v>60.7</v>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D98" s="8" t="inlineStr">
         <is>
           <t>20 / 25</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>Structured patch, pretrained</t>
         </is>
       </c>
-      <c r="B97" s="5" t="n">
+      <c r="B99" s="9" t="n">
         <v>45.6</v>
       </c>
-      <c r="C97" s="5" t="n">
+      <c r="C99" s="9" t="n">
         <v>57.5</v>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>20 / 25</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
         <is>
           <t>Raw DE → logreg</t>
         </is>
       </c>
-      <c r="B98" s="5" t="n">
+      <c r="B100" s="9" t="n">
         <v>51.4</v>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="C100" s="9" t="n">
         <v>62.8</v>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>20 / 25</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
         <is>
           <t>Raw DE + per-series instance norm</t>
         </is>
       </c>
-      <c r="B99" s="5" t="n">
+      <c r="B101" s="9" t="n">
         <v>18</v>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C101" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>20 / 25</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="1" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Reference — PC-SSL leakage audit (accuracy %)</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>Same code, random window split</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D104" s="4" t="inlineStr">
         <is>
           <t>Same code, trial-disjoint split</t>
         </is>
       </c>
-      <c r="E102" s="3" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t>Raw DE → logreg</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>SEED-V</t>
         </is>
       </c>
-      <c r="B103" s="5" t="n">
+      <c r="B105" s="9" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="C103" s="5" t="n">
+      <c r="C105" s="9" t="n">
         <v>65.8</v>
       </c>
-      <c r="D103" s="5" t="n">
+      <c r="D105" s="9" t="n">
         <v>39.8</v>
       </c>
-      <c r="E103" s="5" t="n">
+      <c r="E105" s="9" t="n">
         <v>51.4</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>SEED-IV</t>
         </is>
       </c>
-      <c r="B104" s="5" t="n">
+      <c r="B106" s="9" t="n">
         <v>84.5</v>
       </c>
-      <c r="C104" s="5" t="n">
+      <c r="C106" s="9" t="n">
         <v>70.40000000000001</v>
       </c>
-      <c r="D104" s="5" t="n">
+      <c r="D106" s="9" t="n">
         <v>44.7</v>
       </c>
-      <c r="E104" s="5" t="n">
+      <c r="E106" s="9" t="n">
         <v>62.8</v>
       </c>
     </row>
@@ -2034,272 +2063,272 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Final method (proposed for the paper)</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Alternatives we measured</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Decision / note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>A. What the model is</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Architecture</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Structured-token causal decoder transformer: TimesFM-2.5 decoder layers (RoPE, SDPA), d=256, 6 layers, 8 heads, ~2.4M params; linear token embedder; per-epoch classification head.</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Frozen TimesFM-2.5 stack (E1b), frozen random 1280x20 stack (F3): neither beats the small from-scratch stack.</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Fixed.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Token</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>One token = one labelled epoch; the whole (channels x features) matrix, flattened. FINAL: tf64 = 64 log-spaced Welch log-power bins per channel (sleep 2x64=128-d).</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>DE (5 bands/channel; the proposal's token) -&gt; 75.5 sleep; raw 200 ms tokens (2x20 samples, 150 tokens/epoch) -&gt; 75.5; per-electrode raw -&gt; 76.4.</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>DISCUSS: tf64 is +2.3 over DE on sleep but gives no headroom on seizure (tf64 ladder on CHB-MIT skipped). Paper can present DE as the proposal's token and tf64 as the improved front end.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Normalisation</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Fixed per-(channel,feature) corpus standardisation; NO per-series instance norm (RevIN).</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Instance norm collapses raw DE to chance (51.4-&gt;18.0 SEED-V, 62.8-&gt;26.8 SEED-IV).</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>Fixed (Phase-1 lesson).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Causality</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Causal (each epoch sees only the past) -&gt; streaming-capable, 1 token per decision with a KV cache.</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Bidirectional twin: +0.9 offline, -2.8/-5.0 online.</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>Fixed; the streaming result is a selling point.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>B. Training</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Pretraining (the proposal's contribution)</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Input-space predictive coding: predict the next 16 tokens (multi-step MSE), 60 epochs (DE/tf64) / 10 epochs (raw), single dataset, no labels. Worth +2.5 (DE) / +0.85 (tf64) / +1.2 (raw) on sleep, ~0 on seizure, fine-tuned.</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Latent-target (JEPA/data2vec) objective and 5 variants: worse than input-PC (73.7 vs 75.5 sleep); masked reconstruction (F9): same null on emotion. Random init: within 0.85-2.5 points.</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>DISCUSS: keep pretraining as part of 'the method' (small positive on sleep) or present the model as trained from scratch with pretraining as an ablation? Recommendation: report both columns everywhere; call the final method 'pretrained' only if we keep the sleep +0.85..+2.5 as a claim.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Downstream training</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>End-to-end fine-tuning (encoder + head), class-weighted CE, AdamW 1e-4, nights/files chunked (400 epochs DE/tf64; 20 epochs raw), 8 epochs (sleep DE/tf64), 3 (raw), 4 (seizure).</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Frozen encoder + logistic regression (the July protocol): inflates pretraining 3-12x.</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>Fixed: fine-tuned numbers only in the paper; frozen shown once as the inflation example.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>C. Evaluation</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Sleep-EDF Cassette, 153 nights / 78 subjects / 195k epochs, Fpz-Cz + Pz-Oz, 5 classes (W/N1/N2/N3/REM), 30-min wake trimming, subject-disjoint 5-fold (seed 42 split); acc / macro-F1 / kappa; pretraining seeds 42,1,2,3.</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr"/>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr"/>
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>Fixed.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Seizure</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>CHB-MIT, 24 patients / 682 files / 1.76M 2-s epochs (0.32% seizure), 18-ch bipolar core montage, leave-one-patient-out; bal-acc / sens / spec / ROC-AUC, class-weighted; per-patient paired tests.</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr"/>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr"/>
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Fixed.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Emotion / MI</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>SEED-IV (smoothed + un-smoothed), PC-SSL subject-dependent folds; BCI-IV-2a session hold-out. Frozen-probe only (never fine-tuned).</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr"/>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr"/>
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>DISCUSS: keep as 'where the encoder does not help' (frozen) or drop/appendix.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Controls reported with every result</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>matched random-init (same architecture, same seed); raw-features-&gt;logreg; best non-deep baseline (HGB); dimension-matched random projection (frozen).</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr"/>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr"/>
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>Fixed.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>D. Naming</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Names in tables</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>PhysioFM (pretrained) = physiofm_pc; PhysioFM (no pretrain) = physiofm_rand; PhysioFM (latent) = physiofm_latent; raw features -&gt; logreg = raw_de / raw_tf64.</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr"/>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr"/>
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>DISCUSS: 'PhysioFM' implies a foundation model (no joint pretraining, no zero-shot transfer was done). Keep or rename?</t>
         </is>
@@ -2342,885 +2371,885 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Task</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Dataset / protocol</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Input tokens</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Final method: PhysioFM (pretrained)</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>PhysioFM (no pretrain)</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Pretraining delta</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>raw features -&gt; logreg</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Best non-deep baseline (HGB)</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Published SOTA (UNVERIFIED web figures)</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Seeds</t>
         </is>
       </c>
-      <c r="L1" s="8" t="inlineStr">
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>Include in paper?</t>
         </is>
       </c>
-      <c r="N1" s="8" t="inlineStr">
+      <c r="N1" s="13" t="inlineStr">
         <is>
           <t>Notes for discussion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Per-epoch tasks, FINE-TUNED (the protocol we report)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Sleep staging</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Sleep-EDF-78, subject-disjoint 5-fold</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>tf64 (2x64)</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>acc % (kappa)</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>77.9 +- 0.4 (k .71)</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>77.0 +- 0.2 (k .69)</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>+0.85 (sign consistent 4/4 seeds)</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>72.8 (k .64)</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="J3" s="10" t="inlineStr">
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t>81-85 (k .77-.83) raw-signal models</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>4 pretraining seeds</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="L3" s="15" t="inlineStr">
         <is>
           <t>results/phase4/gate0/sleep_edf_tf64/finetune.csv; EXP-0020</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N3" s="10" t="inlineStr">
+      <c r="N3" s="15" t="inlineStr">
         <is>
           <t>Headline number. Below SOTA by 3-7 with 2.4M params / spectral tokens.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Sleep staging</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Sleep-EDF-78, subject-disjoint 5-fold</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>DE (2x5) — the proposal's token</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>acc % (kappa)</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>75.5 +- 0.3 (k .672)</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>73.1 +- 0.5 (k .645)</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>+2.5 (4/4 seeds)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>67.9 (k .575)</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>69.6</t>
         </is>
       </c>
-      <c r="J4" s="10" t="inlineStr">
+      <c r="J4" s="15" t="inlineStr">
         <is>
           <t>81-85</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="K4" s="15" t="inlineStr">
         <is>
           <t>4 pretraining seeds</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr">
+      <c r="L4" s="15" t="inlineStr">
         <is>
           <t>results/phase4/gate1/sleep_edf/finetune.csv; EXP-0017 4b, EXP-0021</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N4" s="10" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>The proposal's pipeline; shows the DE-&gt;tf64 gain (+2.3) and that pretraining shrinks as input gets richer.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Sleep staging</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Sleep-EDF-78, subject-disjoint 5-fold</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>raw EEG 200 ms (2x20), 150 tok/epoch</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>acc % (kappa)</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>75.5 (k .676)</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>74.2 (k .658)</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>+1.2 (frozen: +14.7)</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="J5" s="15" t="inlineStr">
         <is>
           <t>81-85</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="15" t="inlineStr">
         <is>
           <t>1 seed; 10 pretrain + 3 FT epochs</t>
         </is>
       </c>
-      <c r="L5" s="10" t="inlineStr">
+      <c r="L5" s="15" t="inlineStr">
         <is>
           <t>results/phase4/gate2/sleep_edf_raw/finetune.csv; EXP-0022</t>
         </is>
       </c>
-      <c r="M5" s="12" t="inlineStr">
+      <c r="M5" s="17" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="N5" s="10" t="inlineStr">
+      <c r="N5" s="15" t="inlineStr">
         <is>
           <t>Parity with DE, below tf64 at this budget. Single seed — say so, or run 2 more seeds (~1.5 h on a pod).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Sleep staging — streaming</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Sleep-EDF-78, same folds, DE tokens</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>acc % online (only past visible) / offline</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>75.4 / 75.4 (causal, pretrained)</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>73.2 / 73.2 (causal, no pretrain); bidirectional twin 70.4 online / 74.1 offline</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>causal beats bidirectional online by +2.8 (no pretrain) / +5.0 (pretrained)</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="10" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t>1 seed, 5 folds</t>
         </is>
       </c>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="L6" s="15" t="inlineStr">
         <is>
           <t>results/phase4/gate3/streaming.csv; EXP-0023</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="N6" s="15" t="inlineStr">
         <is>
           <t>The 'defensible claim' of the causal design; 1 token/decision (KV cache) vs 190.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Seizure detection</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>CHB-MIT, 24 patients, leave-one-patient-out</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>DE (18x5)</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>bal-acc % / ROC-AUC</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t>78.4 / .863 (Aug seed 42); 78.2 / .867 (Jul, 3 seeds)</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t>80.2 / .874 (seed 42); 79.1 / .860 (Jul, 3 seeds)</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t>≈ 0 (within +-12 per-patient sd)</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t>72.4 / .806</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t>74.0 / .851</t>
         </is>
       </c>
-      <c r="J7" s="10" t="inlineStr">
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t>AUC .91-.99 (cross-patient; verify)</t>
         </is>
       </c>
-      <c r="K7" s="10" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t>3 seeds (Jul) + 1 (Aug)</t>
         </is>
       </c>
-      <c r="L7" s="10" t="inlineStr">
+      <c r="L7" s="15" t="inlineStr">
         <is>
           <t>results/phase3/f17/f17_ft_seed*.csv; results/phase4/gate1/chbmit/finetune.csv; EXP-0017 4c, EXP-0021</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="M7" s="16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr">
+      <c r="N7" s="15" t="inlineStr">
         <is>
           <t>Architecture beats raw-DE by ~+6 bal-acc / +.06 AUC; pretraining adds nothing. tf64 gives no headroom here (linear 72.4 = 72.4).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Frozen-probe settings (never fine-tuned) — report as scope / failure cases, not headlines</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Emotion, smoothed</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>SEED-IV de_LDS, PC-SSL subject-dependent folds</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>DE (62x5)</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>acc %</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>59.3</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>56.9</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>+2.4</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>62.8</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>(nonlinear &lt;= linear, F10)</t>
         </is>
       </c>
-      <c r="J9" s="10" t="inlineStr">
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t>84.5 published -&gt; 44.7 clean (leakage)</t>
         </is>
       </c>
-      <c r="K9" s="10" t="inlineStr">
+      <c r="K9" s="15" t="inlineStr">
         <is>
           <t>3 seeds</t>
         </is>
       </c>
-      <c r="L9" s="10" t="inlineStr">
+      <c r="L9" s="15" t="inlineStr">
         <is>
           <t>results/phase3/parity; EXP-0016</t>
         </is>
       </c>
-      <c r="M9" s="12" t="inlineStr">
+      <c r="M9" s="17" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="N9" s="10" t="inlineStr">
+      <c r="N9" s="15" t="inlineStr">
         <is>
           <t>Pretrained = random 256-d projection (dim-matched -0.2). Below raw features.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Emotion, un-smoothed</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>SEED-IV de_movingAve, same folds</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>DE (62x5)</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>acc %</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>51.7</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>40.7</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>+11.0 (frozen only)</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>55.3</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="10" t="inlineStr">
+      <c r="J10" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K10" s="10" t="inlineStr">
+      <c r="K10" s="15" t="inlineStr">
         <is>
           <t>3 seeds</t>
         </is>
       </c>
-      <c r="L10" s="10" t="inlineStr">
+      <c r="L10" s="15" t="inlineStr">
         <is>
           <t>results/phase3/parity; EXP-0016</t>
         </is>
       </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="17" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="N10" s="10" t="inlineStr">
+      <c r="N10" s="15" t="inlineStr">
         <is>
           <t>The 'smoothing flip'; still below raw features.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Motor imagery</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>BCI-IV-2a, session hold-out, 9 subj</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>DE (22x5)</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>acc %</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>41.7</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>43.5</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>-1.8</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>51.1</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J11" s="10" t="inlineStr">
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t>~70-85 (raw-signal)</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t>3 seeds</t>
         </is>
       </c>
-      <c r="L11" s="10" t="inlineStr">
+      <c r="L11" s="15" t="inlineStr">
         <is>
           <t>results/phase3/parity/f16*; EXP-0014/0016</t>
         </is>
       </c>
-      <c r="M11" s="12" t="inlineStr">
+      <c r="M11" s="17" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="N11" s="10" t="inlineStr">
+      <c r="N11" s="15" t="inlineStr">
         <is>
           <t>Encoder hurts (dim-matched -9.3). Trial-constant labels.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Seizure prediction (pre-ictal vs interictal)</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>CHB-MIT, patient-specific leave-one-seizure-out, 21 patients / 140 events</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>DE (18x5)</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>bal-acc % / AUC</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>66.8 / .769</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="15" t="inlineStr">
         <is>
           <t>71.3 / .793</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="15" t="inlineStr">
         <is>
           <t>-4.6 / -.024</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="15" t="inlineStr">
         <is>
           <t>65.2 / .710</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I12" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J12" s="10" t="inlineStr">
+      <c r="J12" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K12" s="10" t="inlineStr">
+      <c r="K12" s="15" t="inlineStr">
         <is>
           <t>1 seed</t>
         </is>
       </c>
-      <c r="L12" s="10" t="inlineStr">
+      <c r="L12" s="15" t="inlineStr">
         <is>
           <t>FINAL_REPORT §5; EXP-0018 (CSV on pod only)</t>
         </is>
       </c>
-      <c r="M12" s="13" t="inlineStr">
+      <c r="M12" s="18" t="inlineStr">
         <is>
           <t>no / appendix</t>
         </is>
       </c>
-      <c r="N12" s="10" t="inlineStr">
+      <c r="N12" s="15" t="inlineStr">
         <is>
           <t>Ran as the falsification test of the 'objective misalignment' mechanism; random-init won. Not comparable to detection.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Reference points</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>Phase 1: univariate TimesFM</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>SEED-IV/V, same folds</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>each (channel,band) trace as a scalar series</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>acc %</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>20-28 (chance)</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>51.4 / 62.8</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J14" s="10" t="inlineStr">
+      <c r="J14" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr">
+      <c r="K14" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="15" t="inlineStr">
         <is>
           <t>docs/PHASE1.md</t>
         </is>
       </c>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="M14" s="16" t="inlineStr">
         <is>
           <t>yes (one line)</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="15" t="inlineStr">
         <is>
           <t>Why structured patching exists: RevIN + flattening destroy the signal. Structured: 46-61.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Leakage audit of PC-SSL</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>SEED-V / SEED-IV, PC-SSL code</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>DE</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>acc %</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>published 92.4 / 84.5; leaky re-run 65.8 / 70.4; clean trial-disjoint 39.8 / 44.7</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>51.4 / 62.8</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J15" s="10" t="inlineStr">
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K15" s="10" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="10" t="inlineStr">
+      <c r="L15" s="15" t="inlineStr">
         <is>
           <t>results/phase2/followup/f12; EXP-0008</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="16" t="inlineStr">
         <is>
           <t>yes (one paragraph)</t>
         </is>
       </c>
-      <c r="N15" s="10" t="inlineStr">
+      <c r="N15" s="15" t="inlineStr">
         <is>
           <t>~80% temporal-neighbour leakage. A replication of Brookshire et al. 2024 — cite it.</t>
         </is>
@@ -3259,1035 +3288,1035 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Ablation / control</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Question it answers</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>Arms and numbers</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>Delta / effect</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>Seeds</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>Verdict</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="J1" s="8" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>Include in paper?</t>
         </is>
       </c>
-      <c r="K1" s="8" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>A. Does pretraining help? (the contribution under test)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="n">
+      <c r="A3" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Pretrained vs matched random-init, FINE-TUNED</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Is predictive-coding pretraining worth anything under the protocol competitors use?</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>Sleep DE / tf64 / raw / per-electrode; seizure DE</t>
         </is>
       </c>
-      <c r="E3" s="10" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>sleep DE 75.5 vs 73.1; tf64 77.9 vs 77.0; raw 75.5 vs 74.2; per-electrode 76.4 vs 74.6; seizure 78.4/.863 vs 80.2/.874 (Jul 3-seed 78.2 vs 79.1)</t>
         </is>
       </c>
-      <c r="F3" s="10" t="inlineStr">
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t>+2.5 / +0.85 / +1.2 / +1.8 on sleep; ≈ 0 on seizure</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t>4 / 4 / 1 / 1 / 3+1</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t>Small positive on sleep, shrinking as input gets richer; null on seizure</t>
         </is>
       </c>
-      <c r="I3" s="10" t="inlineStr">
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t>gate1/sleep_edf/finetune.csv, gate0/sleep_edf_tf64/finetune.csv, gate2/*, gate1/chbmit/finetune.csv, f17_ft_seed*</t>
         </is>
       </c>
-      <c r="J3" s="11" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K3" s="10" t="inlineStr">
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t>THE central ablation; must be in the main table.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="n">
+      <c r="A4" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Frozen probe vs fine-tuned (evaluation protocol)</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>How much did the frozen-probe protocol inflate pretraining?</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>same as 1</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr">
+      <c r="E4" s="15" t="inlineStr">
         <is>
           <t>frozen gaps: DE +9.8, tf64 +11.2, raw +14.7, seizure +8.1; fine-tuned gaps: +2.5, +0.85, +1.2, ≈0</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="F4" s="15" t="inlineStr">
         <is>
           <t>inflation 3-12x</t>
         </is>
       </c>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="G4" s="15" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t>Frozen probes measure the poverty of a random-init feature extractor, not the value of pretraining</t>
         </is>
       </c>
-      <c r="I4" s="10" t="inlineStr">
+      <c r="I4" s="15" t="inlineStr">
         <is>
           <t>EXP-0017 4b-c, EXP-0020-0022</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K4" s="10" t="inlineStr">
+      <c r="K4" s="15" t="inlineStr">
         <is>
           <t>Methodological finding; one figure (bars frozen vs fine-tuned).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="n">
+      <c r="A5" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Dimension-matched control (raw features -&gt; random 256-d nonlinear projection), frozen</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>Is the frozen 'gain' just more dimensions?</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>sleep DE/tf64, emotion, MI</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="15" t="inlineStr">
         <is>
           <t>sleep DE: rand-proj 69.3 vs PC 72.6 (+3.3); tf64: 73.3 vs 76.75 (+3.5); emotion 60.2 vs 60.0 (-0.2); MI 49.9 vs 40.6 (-9.3); concat raw+PC: +5.4 sleep, -0.3 emotion, -7.3 MI</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t>see arms</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t>Pretrained encoder adds information only on sleep; on emotion it equals a random map</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="15" t="inlineStr">
         <is>
           <t>results/phase3/diagnose_encoder.csv; gate0/diagnose_encoder_tf64.csv; EXP-0017 §3</t>
         </is>
       </c>
-      <c r="J5" s="11" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr"/>
+      <c r="K5" s="15" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n">
+      <c r="A6" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Label fraction under fine-tuning</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>Does the advantage grow when labels are scarce (the SSL signature)?</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>sleep DE, 1/5/10/100% of training labels</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="15" t="inlineStr">
         <is>
           <t>frozen gap 12.7/11.8/10.8/9.8; fine-tuned gap 1.9/2.4/2.4/2.2</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t>flat fine-tuned</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
+      <c r="G6" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="H6" s="15" t="inlineStr">
         <is>
           <t>Label-efficiency signature is a frozen-probe artefact (retracted claim)</t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="I6" s="15" t="inlineStr">
         <is>
           <t>results/phase3/f13/f13_sleep_ft_labelcurve.csv; EXP-0017 4d</t>
         </is>
       </c>
-      <c r="J6" s="12" t="inlineStr">
+      <c r="J6" s="17" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="15" t="inlineStr">
         <is>
           <t>Mention as part of #2 or drop; do NOT claim 20x/100x.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>B. Which pretraining objective?</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n">
+      <c r="A8" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>Input-space PC vs latent-target PC (JEPA/data2vec style)</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>Is input-space MSE the reason pretraining fails (R2)?</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>sleep DE (4 seeds), seizure, tf64, raw</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="15" t="inlineStr">
         <is>
           <t>sleep DE: input 75.5 vs latent 73.7 vs rand 73.1; seizure 78.4 vs 79.7 vs 80.2; tf64 77.9 vs 77.3 vs 77.0; raw 75.5 vs 74.7 vs 74.2</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t>latent -1.9 vs input-PC on sleep DE; ≈ random elsewhere</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="15" t="inlineStr">
         <is>
           <t>4/1/4/1</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="H8" s="15" t="inlineStr">
         <is>
           <t>Latent targets do not help; objective degenerates into smoothness on per-epoch corpora (skill &lt;= 0)</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="I8" s="15" t="inlineStr">
         <is>
           <t>gate1/*, EXP-0021</t>
         </is>
       </c>
-      <c r="J8" s="11" t="inlineStr">
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>yes (short)</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr"/>
+      <c r="K8" s="15" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Latent objective variants</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>Any latent variant that works?</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>sleep DE, seed 42, fine-tuned</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
         <is>
           <t>delta targets 73.9; cosine/no-norm 72.7 (collapses); variance term 73.2; EMA .99 74.0; p_out 4 74.0 (input-PC 75.4, rand 73.2)</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t>all at random-init level</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="15" t="inlineStr">
         <is>
           <t>gate1/sleep_edf/finetune.csv (variant rows); EXP-0021</t>
         </is>
       </c>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>appendix</t>
         </is>
       </c>
-      <c r="K9" s="10" t="inlineStr"/>
+      <c r="K9" s="15" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Masked reconstruction vs forecasting (F9)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>Is it the temporal objective?</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>emotion smoothed / un-smoothed, frozen</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>both objectives null on smoothed, both ~+9 over random on un-smoothed</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>no difference</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="15" t="inlineStr">
         <is>
           <t>Not the specific objective</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="15" t="inlineStr">
         <is>
           <t>results/phase2/followup/f9; EXP-0011</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="J10" s="19" t="inlineStr">
         <is>
           <t>appendix</t>
         </is>
       </c>
-      <c r="K10" s="10" t="inlineStr"/>
+      <c r="K10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Pretext diagnostics</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Is the pretext learned, and does pretext skill predict transfer?</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>all datasets</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>input-space model/persistence: sleep .60, seizure .57, emo-raw .44, MI .35, emo-smooth 27.8 (degenerate); latent skill vs best trivial: sleep -0.2, seizure -0.6, tf64 ~0, raw +0.36, emotion +0.4/+0.6, MI +0.6</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>skill anti-correlates with transfer (both objectives)</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>1-3</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t>Pretext learned but misaligned; mechanism's falsifiable prediction (seizure prediction) failed</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t>results/phase3/diagnose_pretext.csv; gate1/diagnose_pretext_latent.csv; EXP-0017 4e, 0018, 0021</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t>Scientifically the most interesting part; fits Option B/C.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>C. Which input tokens?</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>DE vs tf64 vs raw tokens (architecture, no pretraining)</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>What does the input representation buy the architecture?</t>
         </is>
       </c>
-      <c r="D13" s="10" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>sleep, fine-tuned</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>random-init: DE 73.1, tf64 77.0, raw 74.2; linear ceilings: DE 67.9, tf64 72.8</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>tf64 +3.9 over DE for the same architecture</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
         <is>
           <t>4/4/1</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>tf64 is the better front end on sleep; none on seizure (linear 72.4 = 72.4)</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I13" s="15" t="inlineStr">
         <is>
           <t>gate0/saturation_*.csv; finetune csvs; EXP-0020</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J13" s="16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K13" s="10" t="inlineStr">
+      <c r="K13" s="15" t="inlineStr">
         <is>
           <t>Gate 0.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n">
+      <c r="A14" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>Linear-saturation test (logreg vs MLP vs HGB)</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <t>Is there nonlinear headroom in the features at all?</t>
         </is>
       </c>
-      <c r="D14" s="10" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>sleep + seizure, DE + tf64</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>sleep DE 67.9/67.2/69.6; tf64 72.8/71.9/75.2; seizure DE 72.4/69.5/74.0 (AUC .807/.824/.851); tf64 72.4/69.9/72.6</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F14" s="15" t="inlineStr">
         <is>
           <t>headroom +1.7 -&gt; +2.3 sleep; +1.6 -&gt; +0.2 seizure</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>5 folds / 24 pat</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>Little headroom on DE; tf64 adds some on sleep only</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I14" s="15" t="inlineStr">
         <is>
           <t>gate0/saturation_*; EXP-0010 (emotion), EXP-0020</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
+      <c r="J14" s="16" t="inlineStr">
         <is>
           <t>yes (one table)</t>
         </is>
       </c>
-      <c r="K14" s="10" t="inlineStr"/>
+      <c r="K14" s="15" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>Structured multi-channel tokens vs per-electrode decomposition (BrainGPT-style)</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Is spatial structure in the token what matters?</t>
         </is>
       </c>
-      <c r="D15" s="10" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>sleep raw tokens, 2 channels</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>structured 75.5/74.7/74.2 vs per-electrode 76.4/75.5/74.6 (PC/latent/rand, fine-tuned); frozen 70.8 vs 72.7</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="15" t="inlineStr">
         <is>
           <t>per-electrode &gt;= structured by ~1</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>Not supported on 2-channel sleep; needs a many-channel corpus</t>
         </is>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t>gate2/*; EXP-0022</t>
         </is>
       </c>
-      <c r="J15" s="12" t="inlineStr">
+      <c r="J15" s="17" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="K15" s="10" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t>Honest limitation; do NOT claim structured &gt; per-electrode.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n">
+      <c r="A16" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Smoothing flip (LDS-smoothed vs un-smoothed DE)</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Does smoothing hide the dynamics PC needs?</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>SEED-IV emotion, frozen, same trials</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="15" t="inlineStr">
         <is>
           <t>within-trial variance 0.08% vs 17.6%; PC - rand +2.4 vs +11.0</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="15" t="inlineStr">
         <is>
           <t>+8.6 from removing smoothing</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>Pretraining needs dynamics in the tokens — but still below raw features</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I16" s="15" t="inlineStr">
         <is>
           <t>EXP-0001, EXP-0016</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="17" t="inlineStr">
         <is>
           <t>discuss</t>
         </is>
       </c>
-      <c r="K16" s="10" t="inlineStr"/>
+      <c r="K16" s="15" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>Context length / horizon (F5) and scale (F6)</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>Do longer context and multi-horizon help?</t>
         </is>
       </c>
-      <c r="D17" s="10" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>un-smoothed SEED-IV, frozen GRU readout</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>PC-rand gap grows with p_in (5.3 -&gt; 18.1 at p_in 8/p_out 16); scale-stable 1M-15M (5 -&gt; 13 -&gt; 13)</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="10" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>Only on un-smoothed DE; frozen readout</t>
         </is>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>EXP-0005, EXP-0006</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" s="19" t="inlineStr">
         <is>
           <t>appendix</t>
         </is>
       </c>
-      <c r="K17" s="10" t="inlineStr"/>
+      <c r="K17" s="15" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>D. Architecture controls</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>Causal vs bidirectional twin, offline vs online</t>
         </is>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>What does causality cost / buy?</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>sleep DE, fine-tuned, same folds</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
         <is>
           <t>causal rand 73.2/73.2; bidir rand 74.1/70.4; causal latent 74.1/74.1; causal PC 75.4/75.4</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="F19" s="15" t="inlineStr">
         <is>
           <t>offline -0.9; online +2.8 (+5.0 pretrained); 1 vs 190 tokens per decision</t>
         </is>
       </c>
-      <c r="G19" s="10" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>Causal wins under a streaming constraint</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I19" s="15" t="inlineStr">
         <is>
           <t>gate3/streaming.csv; EXP-0023</t>
         </is>
       </c>
-      <c r="J19" s="11" t="inlineStr">
+      <c r="J19" s="16" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="K19" s="10" t="inlineStr">
+      <c r="K19" s="15" t="inlineStr">
         <is>
           <t>Gate 3.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="15" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>Per-series instance norm (RevIN) control</t>
         </is>
       </c>
-      <c r="C20" s="10" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Why Phase 1 failed / why no instance norm</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D20" s="15" t="inlineStr">
         <is>
           <t>emotion raw DE -&gt; logreg</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E20" s="15" t="inlineStr">
         <is>
           <t>SEED-V 51.4 -&gt; 18.0; SEED-IV 62.8 -&gt; 26.8 (chance 20/25)</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="F20" s="15" t="inlineStr">
         <is>
           <t>collapse to chance</t>
         </is>
       </c>
-      <c r="G20" s="10" t="inlineStr">
+      <c r="G20" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>Instance norm deletes the discriminative absolute level</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I20" s="15" t="inlineStr">
         <is>
           <t>docs/PHASE2.md E3.2</t>
         </is>
       </c>
-      <c r="J20" s="11" t="inlineStr">
+      <c r="J20" s="16" t="inlineStr">
         <is>
           <t>yes (one line)</t>
         </is>
       </c>
-      <c r="K20" s="10" t="inlineStr"/>
+      <c r="K20" s="15" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>Frozen random stack vs frozen TimesFM stack (F3); matched MLP head (F4)</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>Do TimesFM weights transfer? Is the head the limiter?</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>emotion, frozen</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
         <is>
           <t>random 1280x20 stack 47.3/58.9 vs TimesFM 43.3/60.4; MLP head stays in the 41-55 band</t>
         </is>
       </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="F21" s="15" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="15" t="inlineStr">
         <is>
           <t>TimesFM weights add nothing; head not the lever</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I21" s="15" t="inlineStr">
         <is>
           <t>EXP-0003, EXP-0004</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J21" s="19" t="inlineStr">
         <is>
           <t>appendix</t>
         </is>
       </c>
-      <c r="K21" s="10" t="inlineStr"/>
+      <c r="K21" s="15" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="15" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>Order-shuffle control</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>Is the sleep gain temporal?</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>sleep frozen; emotion/MI</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>sleep PC 72.6 -&gt; 67.4 (= raw-DE level), raw unchanged; on trial-constant-label tasks shuffling HELPS (+7.4 emotion) -&gt; uninterpretable there</t>
         </is>
       </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>-5.2 on sleep</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr">
+      <c r="G22" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="15" t="inlineStr">
         <is>
           <t>Frozen sleep gain is temporal; control valid only for per-epoch labels</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr">
         <is>
           <t>EXP-0009 4e, EXP-0016</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J22" s="19" t="inlineStr">
         <is>
           <t>appendix</t>
         </is>
       </c>
-      <c r="K22" s="10" t="inlineStr"/>
+      <c r="K22" s="15" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="15" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>Data-only predictability (tau) vs gain</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Can a raw-data score predict the SSL gain?</t>
         </is>
       </c>
-      <c r="D23" s="10" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>5 settings</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
         <is>
           <t>MI has the highest tau (0.27) and no gain; sleep the lowest among positives and the largest frozen gain</t>
         </is>
       </c>
-      <c r="F23" s="10" t="inlineStr">
+      <c r="F23" s="15" t="inlineStr">
         <is>
           <t>no correlation</t>
         </is>
       </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="G23" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="15" t="inlineStr">
         <is>
           <t>No (kills the 'temporal learnability' framing)</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I23" s="15" t="inlineStr">
         <is>
           <t>results/phase3/temporal_structure.csv; EXP-0016</t>
         </is>
       </c>
-      <c r="J23" s="13" t="inlineStr">
+      <c r="J23" s="18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="K23" s="10" t="inlineStr"/>
+      <c r="K23" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4316,242 +4345,242 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Statement</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Why it is out</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>What we say instead</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Pretraining gives +9.8 (sleep) / +14.5 / +8.1 (seizure)</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>frozen-probe numbers</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="15" t="inlineStr">
         <is>
           <t>fine-tuned: +2.5 / ≈0</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="15" t="inlineStr">
         <is>
           <t>report fine-tuned; frozen once as the inflation example</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>20x / 100x label efficiency</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>frozen-probe artefact</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>fine-tuned gap flat +1.9..+2.4 at 1-100% labels</t>
         </is>
       </c>
-      <c r="D3" s="10" t="inlineStr">
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t>drop</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>PC helps in proportion to temporal structure</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>MI has the highest predictability and no gain; seizure prediction falsified the refined version</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
+      <c r="C4" s="15" t="inlineStr">
         <is>
           <t>EXP-0016, EXP-0018</t>
         </is>
       </c>
-      <c r="D4" s="10" t="inlineStr">
+      <c r="D4" s="15" t="inlineStr">
         <is>
           <t>drop</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>The objective-misalignment mechanism explains the failure</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>its falsifiable prediction (seizure prediction) failed</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>rand .793 &gt; PC .769 AUC</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t>report the diagnostic (pretext skill anti-correlates with transfer) without asserting the mechanism</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Structured spatial patching beats per-electrode decomposition</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>2-channel sleep shows the opposite</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>76.4 vs 75.5</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>limitation: needs a many-channel corpus</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>A foundation model / cross-task transfer</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>joint multi-dataset pretraining and zero-shot transfer were never run</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>proposal Phase 3</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>future work; consider renaming</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Beats / matches published SOTA</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>below on every task; SOTA figures unverified</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>sleep 77.9 vs 81-85; seizure AUC .87 vs .91-.99</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="15" t="inlineStr">
         <is>
           <t>honest positioning table after verifying numbers; emphasise 2.4M params, spectral tokens, streaming</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>The leakage audit is a new finding</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>Brookshire et al. 2024 documented EEG segment-split leakage with similar numbers</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>ICML_proposal.md §B</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>replication + mechanism, cite Brookshire</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Latent-target / raw-EEG / richer tokens rescue pretraining</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Gates 0-2</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <t>+0.85 / +1.2 / latent -1.9</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>state as tested and negative</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Seizure prediction is a result</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>single seed, patient-specific, run only as a falsification test</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>EXP-0018</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>appendix at most</t>
         </is>

--- a/docs/paper_results_tables.xlsx
+++ b/docs/paper_results_tables.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numbers" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main results" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablations" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do not claim" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main (Aug 27)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numbers" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main results" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do not claim" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +54,26 @@
       <color rgb="005B6579"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -91,8 +110,18 @@
         <fgColor rgb="00F9E5E5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EEDC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -114,11 +143,16 @@
         <color rgb="00D5DAE4"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -169,6 +203,24 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -534,6 +586,323 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>PhysioFM-S — one recipe (spectral tokens + causal decoder + end-to-end fine-tune), zero per-dataset tuning. Green = final method; grey = matched no-pretrain control.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="21" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>Protocol</t>
+        </is>
+      </c>
+      <c r="C3" s="21" t="inlineStr">
+        <is>
+          <t>Metrics</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>Random-init</t>
+        </is>
+      </c>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>PC-pretrained</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>Best published</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="inlineStr">
+        <is>
+          <t>One-line story</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Sleep-EDF-78</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>5-fold subject-disjoint</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>acc / κ</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>77.0 / .69</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>77.9 ± 0.4 / .71</t>
+        </is>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>84.9 / .789 (SleepTransformer, bidirectional offline)</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>causality costs ≈1 pt (measured); rest = epoch encoder</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>HMC (151 subj, NEW)</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>fixed published split (NeuroLM)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>bal-acc / κ</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>73.8 / .668</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>73.8 ± 0.9 / .668 (8 seeds)</t>
+        </is>
+      </c>
+      <c r="F5" s="22" t="inlineStr">
+        <is>
+          <t>.740 / .698 (REVE-Base; EEG foundation models)</t>
+        </is>
+      </c>
+      <c r="G5" s="22" t="inlineStr">
+        <is>
+          <t>2nd of 8 on bal-acc at ~1/100th params</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Physio2018 (994 subj, NEW)</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>SleePyCo's exact folds</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>acc / κ</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>76.1 / .684</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>76.1 / .684</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>80.9 / .737 (SleePyCo, bidirectional offline)</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>channels +1.9, context ≤1 (measured); rest = epoch encoder</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>CHB-MIT seizure (24 pat)</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>leave-one-patient-out</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>bal-acc / AUC</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>80.2 / .874</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>78.4 / .863</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>AUC .91–.99 (verify)</t>
+        </is>
+      </c>
+      <c r="G7" s="22" t="inlineStr">
+        <is>
+          <t>architecture +6 over raw-DE; pretraining ≈ 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>TRANSFER: P2018 → Sleep-EDF</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>per-electrode tokens, 5-fold</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>78.4  (+3.1 ± 0.3, 4 replicates)</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>≈ same-corpus pretraining (77.8)</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>pretraining pays under domain shift — proposal Phase 3, done</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>STREAMING (past-only decisions)</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Sleep-EDF 5-fold</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>bidirectional: 74.1 offline → 70.4 online</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>causal: 75.4 online = offline</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>the causal model's home turf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>Takeaways: (1) the architecture generalizes — same recipe, 3 sleep corpora + seizure; competitive with billion-token EEG foundation models on HMC's fixed split.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>(2) In-domain pretraining Δ ≈ 0 everywhere, up to 994 subjects — consistent with published SSL sleep results (BENDR, mulEEG): a finding, not a failure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>(3) Pretraining pays exactly where the literature says: cross-corpus transfer +3.1 (all 4 replicates positive) = the proposal's Phase-3 claim, delivered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Metric families follow each benchmark's convention (acc/κ vs bal-acc/κ vs bal-acc/AUC) — never mix across rows. Sleep-EDF uses the standard ±30-min convention.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2047,7 +2416,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2345,7 +2714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3258,14 +3627,14 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A13:N13"/>
+    <mergeCell ref="A2:N2"/>
     <mergeCell ref="A8:N8"/>
-    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4329,7 +4698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/paper_results_tables.xlsx
+++ b/docs/paper_results_tables.xlsx
@@ -7,12 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main (Aug 27)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numbers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablations" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do not claim" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simple (Aug 27)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main (Aug 27)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Numbers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Method" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablations" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Do not claim" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -73,7 +74,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -120,6 +121,16 @@
         <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -152,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -221,6 +232,24 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -586,6 +615,231 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>All numbers = % of 30-second windows labeled correctly (higher is better)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="B3" s="28" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="C3" s="28" t="inlineStr">
+        <is>
+          <t>Us</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>Best published</t>
+        </is>
+      </c>
+      <c r="E3" s="28" t="inlineStr">
+        <is>
+          <t>Beat it?</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>Sleep-EDF (78 people)</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>sleep staging</t>
+        </is>
+      </c>
+      <c r="C4" s="30" t="n">
+        <v>77.90000000000001</v>
+      </c>
+      <c r="D4" s="29" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>No  (−7.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>HMC (151 patients)</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>sleep staging</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="n">
+        <v>73.8</v>
+      </c>
+      <c r="D5" s="29" t="n">
+        <v>74</v>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>Tie with #1; above the other 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>Physio2018 (994 people)</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>sleep staging</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>No  (−4.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>CHB-MIT (24 patients)</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>seizure detection</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>~90</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Real-time test</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>decide from past only</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>YES  (+5.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>Transfer test</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>pretrain big → apply to small</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>75.2 (no pretraining)</t>
+        </is>
+      </c>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>YES  (+3.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>1. Rows 1–3: the published winners are big OFFLINE models that also read the future — they cannot run in real time. Row 5 = everyone forced to real time: we win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>2. Row 2: the competitors are EEG foundation models (LaBraM, CBraMod, REVE…) ~100× our size; we land 2nd of 8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>3. Row 6: pretraining does nothing WITHIN a dataset (tested up to 994 people) but gives +3.1 ACROSS datasets — the proposal's Phase-3 result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>(HMC and CHB-MIT rows use class-balanced accuracy — the convention on those benchmarks.)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -897,7 +1151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2416,7 +2670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2714,7 +2968,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3634,7 +3888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4698,7 +4952,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
